--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20211.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="91">
   <si>
     <t>Mat</t>
   </si>
@@ -88,193 +88,205 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
   </si>
   <si>
     <t>MONTERO</t>
   </si>
   <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>NARANJO</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
     <t>OSORIO</t>
   </si>
   <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>NANCY PAOLA</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>ROSA ITZEL</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>CHRISTIAN GABRIEL</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
   </si>
   <si>
     <t>MARIA DEL PILAR</t>
   </si>
   <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>BRYAN ABRAHAM</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>PERLA</t>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>ATZIN HEFZIBA</t>
   </si>
   <si>
     <t>EDNA</t>
   </si>
   <si>
-    <t>ZURISADAI</t>
+    <t>AMISADAI</t>
   </si>
   <si>
     <t>DARLA MARLENE</t>
   </si>
   <si>
-    <t>ANDRIK YOSIMAR</t>
-  </si>
-  <si>
     <t>KARINA YOSELIN</t>
   </si>
   <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>ANGEL SAMUEL</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
-  </si>
-  <si>
-    <t>JONATHAN MOISES</t>
+    <t>ANGEL DE JESUS</t>
   </si>
   <si>
     <t>ABIGAIL</t>
@@ -678,19 +690,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>70.59</v>
+        <v>79.41</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -704,19 +716,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>58.06</v>
+        <v>64.52</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -730,19 +742,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -756,10 +768,10 @@
         <v>43</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>17</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>26</v>
@@ -768,7 +780,7 @@
         <v>60.47</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -782,19 +794,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>62.79</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -808,19 +820,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -834,19 +846,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8">
-        <v>86.11</v>
+        <v>88.89</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -899,16 +911,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>79.41</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -922,16 +937,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
+        <v>13</v>
+      </c>
+      <c r="F3">
         <v>18</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>58.06</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -945,16 +963,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>72.22</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -968,16 +989,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>72.09</v>
+      </c>
+      <c r="H5">
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -991,16 +1015,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>76.73999999999999</v>
+      </c>
+      <c r="H6">
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1014,16 +1041,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H7">
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1037,16 +1067,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H8">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1132,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>70.59</v>
+        <v>79.41</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1125,10 +1158,10 @@
         <v>31</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>13</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -1137,7 +1170,7 @@
         <v>58.06</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1151,19 +1184,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>69.44</v>
+        <v>72.22</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1177,19 +1210,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>60.47</v>
+        <v>72.09</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1203,19 +1236,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>62.79</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1229,19 +1262,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>79.17</v>
+        <v>83.33</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1255,19 +1288,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>86.11</v>
+        <v>75</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1277,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1309,108 +1342,108 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920162</v>
+        <v>21330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920233</v>
+        <v>21330051920212</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920241</v>
+        <v>21330051920213</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920358</v>
+        <v>21330051920250</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920277</v>
+        <v>21330051920284</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1419,21 +1452,21 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920284</v>
+        <v>21330051920288</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1442,21 +1475,21 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920295</v>
+        <v>21330051920294</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1465,21 +1498,21 @@
         <v>14</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920297</v>
+        <v>21330051920299</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1488,21 +1521,21 @@
         <v>14</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920299</v>
+        <v>21330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1511,136 +1544,136 @@
         <v>14</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920304</v>
+        <v>20330051920174</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920324</v>
+        <v>20330051920306</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G12">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920328</v>
+        <v>21330051920159</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920330</v>
+        <v>21330051920173</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920169</v>
+        <v>21330051920192</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920191</v>
+        <v>21330051920209</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1649,30 +1682,30 @@
         <v>11</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920209</v>
+        <v>21330051920230</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1680,13 +1713,13 @@
         <v>21330051920240</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1695,67 +1728,67 @@
         <v>12</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920253</v>
+        <v>21330051920241</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920257</v>
+        <v>21330051920222</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920360</v>
+        <v>21330051920253</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1764,21 +1797,21 @@
         <v>13</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920291</v>
+        <v>21330051920297</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1787,7 +1820,7 @@
         <v>14</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1795,13 +1828,13 @@
         <v>21330051920298</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1810,21 +1843,21 @@
         <v>14</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920319</v>
+        <v>21330051920304</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1833,44 +1866,44 @@
         <v>14</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920342</v>
+        <v>21330051920328</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920353</v>
+        <v>21330051920347</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1879,7 +1912,30 @@
         <v>15</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920353</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20211.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
   <si>
     <t>Mat</t>
   </si>
@@ -88,30 +88,36 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VIVAS</t>
+  </si>
+  <si>
     <t>LORENZO</t>
   </si>
   <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
     <t>DOLORES</t>
   </si>
   <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>NAMORADO</t>
   </si>
   <si>
@@ -133,12 +139,6 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
@@ -157,48 +157,48 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
+    <t>TLAXCALA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
     <t>PIEDRAS</t>
   </si>
   <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
@@ -211,63 +211,60 @@
     <t>OSORIO</t>
   </si>
   <si>
-    <t>CORONA</t>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>GREGORIO</t>
   </si>
   <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>MARIA DEL PILAR</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>NANCY PAOLA</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>ROSA ITZEL</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>CHRISTIAN GABRIEL</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JORGE MARIO</t>
+  </si>
+  <si>
     <t>LUIS REY</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>CARLOS EMILIO</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN GABRIEL</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>MARIA DEL PILAR</t>
-  </si>
-  <si>
     <t>YAEL</t>
   </si>
   <si>
@@ -277,9 +274,6 @@
     <t>EDNA</t>
   </si>
   <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
     <t>DARLA MARLENE</t>
   </si>
   <si>
@@ -287,9 +281,6 @@
   </si>
   <si>
     <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1342,22 +1333,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920386</v>
+        <v>21330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -1365,16 +1356,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920212</v>
+        <v>21330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1383,44 +1374,44 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920213</v>
+        <v>21330051920240</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920250</v>
+        <v>21330051920241</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1429,44 +1420,44 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920284</v>
+        <v>21330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920288</v>
+        <v>21330051920284</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1480,39 +1471,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920294</v>
+        <v>21330051920288</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920299</v>
+        <v>21330051920298</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1529,13 +1520,13 @@
         <v>21330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1544,44 +1535,44 @@
         <v>14</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920174</v>
+        <v>21330051920353</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920306</v>
+        <v>20330051920174</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1595,39 +1586,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920159</v>
+        <v>20330051920306</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920173</v>
+        <v>21330051920159</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1636,44 +1627,44 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920192</v>
+        <v>21330051920173</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920209</v>
+        <v>21330051920192</v>
       </c>
       <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
-        <v>57</v>
-      </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1682,67 +1673,67 @@
         <v>11</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920230</v>
+        <v>21330051920209</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920240</v>
+        <v>21330051920212</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920241</v>
+        <v>21330051920230</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1751,7 +1742,7 @@
         <v>12</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1765,7 +1756,7 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1774,7 +1765,7 @@
         <v>12</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1788,7 +1779,7 @@
         <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1797,7 +1788,7 @@
         <v>13</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1811,7 +1802,7 @@
         <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1820,21 +1811,21 @@
         <v>14</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920298</v>
+        <v>21330051920304</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1843,21 +1834,21 @@
         <v>14</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920304</v>
+        <v>21330051920328</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1866,76 +1857,30 @@
         <v>14</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920328</v>
+        <v>21330051920347</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920347</v>
-      </c>
-      <c r="B26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920353</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20211.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
   <si>
     <t>Mat</t>
   </si>
@@ -121,9 +121,6 @@
     <t>NAMORADO</t>
   </si>
   <si>
-    <t>PARRA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -184,9 +181,6 @@
     <t>CORONA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -242,9 +236,6 @@
   </si>
   <si>
     <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
   </si>
   <si>
     <t>MARIO</t>
@@ -1301,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1339,10 +1330,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1362,10 +1353,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1385,10 +1376,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1408,10 +1399,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1431,10 +1422,10 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1454,10 +1445,10 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1477,10 +1468,10 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1500,10 +1491,10 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1523,10 +1514,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1546,10 +1537,10 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1569,10 +1560,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1586,39 +1577,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920306</v>
+        <v>21330051920159</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920159</v>
+        <v>21330051920173</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1627,27 +1618,27 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920173</v>
+        <v>21330051920192</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1655,16 +1646,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920192</v>
+        <v>21330051920209</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1673,21 +1664,21 @@
         <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920209</v>
+        <v>21330051920212</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1701,22 +1692,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920212</v>
+        <v>21330051920230</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1724,16 +1715,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920230</v>
+        <v>21330051920222</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1742,67 +1733,67 @@
         <v>12</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920222</v>
+        <v>21330051920253</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920253</v>
+        <v>21330051920297</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920297</v>
+        <v>21330051920304</v>
       </c>
       <c r="B22" t="s">
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1811,21 +1802,21 @@
         <v>14</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920304</v>
+        <v>21330051920328</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1834,52 +1825,29 @@
         <v>14</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920328</v>
+        <v>21330051920347</v>
       </c>
       <c r="B24" t="s">
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920347</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20211.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -88,190 +88,91 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VIVAS</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>MONTERO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>RANGEL</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>TLAXCALA</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>DARLA MARLENE</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>MARIA DEL PILAR</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN GABRIEL</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -695,19 +596,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3">
-        <v>64.52</v>
+        <v>62.5</v>
       </c>
       <c r="H3">
         <v>6.4</v>
@@ -828,10 +729,10 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
         <v>32</v>
@@ -916,19 +817,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>18</v>
       </c>
       <c r="G3">
-        <v>58.06</v>
+        <v>56.25</v>
       </c>
       <c r="H3">
         <v>6.4</v>
@@ -1049,10 +950,10 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>27</v>
@@ -1117,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>79.41</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1137,22 +1038,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>58.06</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1169,16 +1070,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>72.22</v>
+        <v>80.56</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1195,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>72.09</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1221,16 +1122,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>76.73999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1247,16 +1148,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1270,19 +1171,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>75</v>
+        <v>80.56</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1292,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1324,39 +1225,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920183</v>
+        <v>21330051920201</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920386</v>
+        <v>21330051920202</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1370,16 +1271,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920240</v>
+        <v>21330051920235</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1388,21 +1289,21 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920241</v>
+        <v>21330051920242</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1411,50 +1312,50 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920250</v>
+        <v>21330051920294</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920284</v>
+        <v>21330051920297</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1462,22 +1363,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920288</v>
+        <v>21330051920304</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1485,369 +1386,70 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920298</v>
+        <v>21330051920353</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920330</v>
+        <v>19330061430023</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920353</v>
+        <v>21330051920241</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920174</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920159</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920173</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920192</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920209</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920212</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920230</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920222</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920253</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920297</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920304</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920328</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920347</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>
